--- a/AAII_Financials/Yearly/SMCI_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SMCI_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
   <si>
     <t>SMCI</t>
   </si>
@@ -656,208 +656,220 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44012</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43646</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43281</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42916</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42551</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42185</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41820</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41455</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>39063100</v>
+      </c>
+      <c r="E8" s="3">
         <v>21972000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>14989300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7123500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5196100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3557400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3339300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3500400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3360500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2484900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2225000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1954400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1467200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1162600</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>34835800</v>
+      </c>
+      <c r="E9" s="3">
         <v>19542100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>12927800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5840500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4396100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3022900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2813100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3004800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2930500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2135000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2136400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1875300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1241700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1002500</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4227300</v>
+      </c>
+      <c r="E10" s="3">
         <v>2429900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2061400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1283000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>800000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>534500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>526200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>495500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>430000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>350000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>88700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>79000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>225500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>160100</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -875,53 +887,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>771200</v>
+      </c>
+      <c r="E12" s="3">
         <v>636600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>463500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>307300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>272300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>224400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>221500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>179900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>165100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>144000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>124200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>101400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>84300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>75200</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -964,20 +980,23 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-16900</v>
+      </c>
+      <c r="E14" s="3">
         <v>27700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1300</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>24</v>
@@ -988,11 +1007,11 @@
       <c r="I14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" s="3">
         <v>2700</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>24</v>
@@ -1000,8 +1019,8 @@
       <c r="M14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1009,39 +1028,42 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>58300</v>
+        <v>53700</v>
       </c>
       <c r="E15" s="3">
-        <v>38700</v>
+        <v>41300</v>
       </c>
       <c r="F15" s="3">
+        <v>29600</v>
+      </c>
+      <c r="G15" s="3">
         <v>34900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>32500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>28200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>28500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>24200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>21800</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1054,9 +1076,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,98 +1096,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>36292600</v>
+      </c>
+      <c r="E17" s="3">
         <v>20719000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13778500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6362300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4860900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3433500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3253600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3403100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3265800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2390100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2117500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1821700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1386900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1135400</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>2770500</v>
+      </c>
+      <c r="E18" s="3">
         <v>1253000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1210800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>761100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>335200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>123900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>85700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>97200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>94700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>94900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>107500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>132600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>80300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>27200</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1180,88 +1212,92 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-39900</v>
+        <v>-7100</v>
       </c>
       <c r="E20" s="3">
-        <v>-25800</v>
+        <v>19900</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-9300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>1351300</v>
+        <v>2831200</v>
       </c>
       <c r="E21" s="3">
-        <v>1275300</v>
+        <v>1274400</v>
       </c>
       <c r="F21" s="3">
+        <v>1237300</v>
+      </c>
+      <c r="G21" s="3">
         <v>796100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>376900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>149500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>117900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>119200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>112200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>109900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>122300</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>24</v>
@@ -1269,144 +1305,156 @@
       <c r="P21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>194600</v>
+      </c>
+      <c r="E22" s="3">
         <v>59600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>19400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>10500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>6400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>6700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>600</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>2786800</v>
+      </c>
+      <c r="E23" s="3">
         <v>1205700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1216000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>750700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>338000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>118800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>87200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>86800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>84600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>91300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>107400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>132600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>79600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>26600</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>556300</v>
+      </c>
+      <c r="E24" s="3">
         <v>156900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>63300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>110700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>52900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>14900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>38400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>24400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>35300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>40100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>25400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5300</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1449,99 +1497,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>2230500</v>
+      </c>
+      <c r="E26" s="3">
         <v>1048900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1152700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>640000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>285200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>111900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>84300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>71900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>46200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>66900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>72100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>92600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>54200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>21300</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>2195800</v>
+      </c>
+      <c r="E27" s="3">
         <v>1048800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1152700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>640000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>285200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>111900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>84300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>71900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>46200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>66900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>72100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>92600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>54100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>21200</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1614,8 +1674,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>24</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>24</v>
@@ -1629,9 +1689,12 @@
       <c r="P29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,99 +1785,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>39900</v>
+        <v>7100</v>
       </c>
       <c r="E32" s="3">
-        <v>25800</v>
+        <v>-19900</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>-3100</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>9300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2230500</v>
+      </c>
+      <c r="E33" s="3">
         <v>1048900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1152700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>640000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>285200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>111900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>84300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>71900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>46200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>66900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>72100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>92600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>54100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>21200</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,104 +1929,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2230500</v>
+      </c>
+      <c r="E35" s="3">
         <v>1048900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1152700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>640000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>285200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>111900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>84300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>71900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>46200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>66900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>72100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>92600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>54100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>21200</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44012</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43646</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43281</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42916</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42551</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42185</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41820</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41455</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,71 +2073,75 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7521500</v>
+      </c>
+      <c r="E41" s="3">
         <v>5169900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1669800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>440500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>267400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>232300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>210500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>248200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>115400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>110600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>178800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>95400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>96900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>93000</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E42" s="3">
         <v>6200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3700</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>300</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -2077,107 +2166,116 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2217700</v>
+        <v>6262600</v>
       </c>
       <c r="E43" s="3">
+        <v>2359200</v>
+      </c>
+      <c r="F43" s="3">
         <v>2749300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1176000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>858900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>563800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>500400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>476700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>544400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>403300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>250700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>330100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>218300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>153400</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>12895900</v>
+      </c>
+      <c r="E44" s="3">
         <v>4680400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4333000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1445600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1545600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1041000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>851500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>670200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>853300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>736700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>516800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>463500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>315800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>254200</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>24</v>
+      <c r="D45" s="3">
+        <v>883800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>59100</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>24</v>
@@ -2185,171 +2283,183 @@
       <c r="G45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I45" s="3">
         <v>23300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>23000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>21400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>25400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>23100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>22600</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>27726300</v>
+      </c>
+      <c r="E46" s="3">
         <v>12301700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8932000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3179400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2806300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1867300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1592800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1421800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1530900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1261200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>954300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>914400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>654100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>523200</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>148000</v>
+      </c>
+      <c r="E47" s="3">
         <v>112400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>61000</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I47" s="3">
         <v>6100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>10200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4000</v>
-      </c>
-      <c r="O47" s="3">
-        <v>3400</v>
       </c>
       <c r="P47" s="3">
         <v>3400</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>3400</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1146800</v>
+      </c>
+      <c r="E48" s="3">
         <v>798200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>448600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>309100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>286000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>294800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>257600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>207300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>196600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>195600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>188500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>163000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>130600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>95900</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2360,11 +2470,11 @@
         <v>0</v>
       </c>
       <c r="F49" s="3">
+        <v>0</v>
+      </c>
+      <c r="G49" s="3">
         <v>1800</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
       <c r="H49" s="3">
         <v>0</v>
       </c>
@@ -2392,9 +2502,12 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,54 +2598,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>185500</v>
+      </c>
+      <c r="E52" s="3">
         <v>21700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>21700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>42900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>48200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>49200</v>
-      </c>
-      <c r="N52" s="3">
-        <v>8300</v>
       </c>
       <c r="O52" s="3">
         <v>8300</v>
       </c>
       <c r="P52" s="3">
+        <v>8300</v>
+      </c>
+      <c r="Q52" s="3">
         <v>9800</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,54 +2694,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>29945500</v>
+      </c>
+      <c r="E54" s="3">
         <v>14018400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9826100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3674700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3205100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2242000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1918600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1682600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1769500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1515100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1191500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1089800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>796300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>632300</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,212 +2785,225 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2247000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1282000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1472400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>776800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>655400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>612300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>417700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>360500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>527200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>396900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>267400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>299800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>219400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>172900</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2080400</v>
+      </c>
+      <c r="E58" s="3">
         <v>96200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>411600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>170100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>449100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>69800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>30000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>23600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>116200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>161400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>53600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>93500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>42600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>28600</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2323800</v>
+      </c>
+      <c r="E59" s="3">
         <v>724900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>310600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>263800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>153100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>202100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>185100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>152300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>117000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>114200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>88700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>60900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>49000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>40200</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7160100</v>
+      </c>
+      <c r="E60" s="3">
         <v>2344800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2345700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1374700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1470000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>968900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>707600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>606000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>811600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>672500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>409600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>454100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>310900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>241700</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7179500</v>
+      </c>
+      <c r="E61" s="3">
         <v>4963000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1771800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>120200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>147600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>49200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>23800</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
@@ -2869,65 +3011,71 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>40000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6500</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>92200</v>
+      </c>
+      <c r="E62" s="3">
         <v>46200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>67900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>37900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>39100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>26600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>23900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>26200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>24600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>68800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>63900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>15700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>12500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>10300</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,54 +3214,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15465900</v>
+      </c>
+      <c r="E66" s="3">
         <v>7716600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4408700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1702600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1779300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1145600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>852900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>741400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>925900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>741500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>495000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>470900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>327300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>258700</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,14 +3378,17 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>4226300</v>
       </c>
       <c r="E70" s="3">
         <v>0</v>
@@ -3259,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,54 +3474,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5651900</v>
+      </c>
+      <c r="E72" s="3">
         <v>3434500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2585700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1433000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>942900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>657800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>696200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>611900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>532300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>486000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>419100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>373900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>272100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>217900</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,54 +3666,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10253200</v>
+      </c>
+      <c r="E76" s="3">
         <v>6301700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5417200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1972000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1425600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1096200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1065500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>941000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>843500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>773700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>696500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>618900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>469100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>373500</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,104 +3762,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44012</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43646</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43281</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42916</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42551</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42185</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41820</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41455</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2230500</v>
+      </c>
+      <c r="E81" s="3">
         <v>1048900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1152700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>640000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>285200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>111900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>84300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>71900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>46200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>66900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>72100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>92600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>54100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>21200</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,43 +3886,44 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>90300</v>
+      </c>
+      <c r="E83" s="3">
         <v>58300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>38700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>34900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>32500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>28200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>28500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>24200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>21800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>16400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>13300</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>24</v>
@@ -3733,9 +3931,12 @@
       <c r="P83" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,54 +4171,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6809900</v>
+      </c>
+      <c r="E89" s="3">
         <v>1659500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2486000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>663600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-440800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>123000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-30300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>262600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>84300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-96200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>108000</v>
-      </c>
-      <c r="N89" s="3">
-        <v>6500</v>
       </c>
       <c r="O89" s="3">
         <v>6500</v>
       </c>
       <c r="P89" s="3">
+        <v>6500</v>
+      </c>
+      <c r="Q89" s="3">
         <v>13600</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,53 +4242,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-162000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-127200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-124300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-36800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-45200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-58000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-44300</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-24800</v>
       </c>
       <c r="K91" s="3">
         <v>-24800</v>
       </c>
       <c r="L91" s="3">
+        <v>-24800</v>
+      </c>
+      <c r="M91" s="3">
         <v>-29400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-34100</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-40600</v>
       </c>
       <c r="O91" s="3">
         <v>-40600</v>
       </c>
       <c r="P91" s="3">
+        <v>-40600</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,44 +4383,47 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-200300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-183200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-194200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-39500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-46300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-58000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-43600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-24800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-25900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-29400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-35100</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>24</v>
@@ -4202,9 +4431,12 @@
       <c r="P94" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,8 +4454,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4266,9 +4499,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,44 +4643,47 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>9478800</v>
+      </c>
+      <c r="E100" s="3">
         <v>2024000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3911700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-448300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>522900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-44400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>23800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-95800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-50800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>57700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>13100</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>24</v>
@@ -4446,44 +4691,47 @@
       <c r="P100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E101" s="3">
         <v>1700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-3400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-100</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>24</v>
@@ -4491,52 +4739,58 @@
       <c r="P101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2459200</v>
+      </c>
+      <c r="E102" s="3">
         <v>3502000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1229300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>172400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>35100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>21100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-49800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>141800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-67900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>85900</v>
-      </c>
-      <c r="N102" s="3">
-        <v>3800</v>
       </c>
       <c r="O102" s="3">
         <v>3800</v>
       </c>
       <c r="P102" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Q102" s="3">
         <v>12200</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
